--- a/反义词.xlsx
+++ b/反义词.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19500" windowHeight="9144"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="181">
   <si>
     <t>引く</t>
   </si>
@@ -560,6 +560,21 @@
   </si>
   <si>
     <t>ざつおん</t>
+  </si>
+  <si>
+    <t>充足的</t>
+  </si>
+  <si>
+    <t>たっぷり</t>
+  </si>
+  <si>
+    <t>不够的</t>
+  </si>
+  <si>
+    <t>たりない</t>
+  </si>
+  <si>
+    <t>足りない</t>
   </si>
 </sst>
 </file>
@@ -608,9 +623,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1060,19 +1074,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1081,7 +1095,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1205,12 +1219,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1530,7 +1545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:F84"/>
+  <dimension ref="A2:F86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -2247,7 +2262,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="81" ht="18" spans="1:5">
+    <row r="81" ht="18" spans="1:6">
       <c r="A81" s="3" t="s">
         <v>168</v>
       </c>
@@ -2261,7 +2276,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -2269,12 +2284,30 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
       <c r="B84" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="86" ht="18" spans="1:6">
+      <c r="A86" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
